--- a/final_data_pipeline/output/325212_elec_options.xlsx
+++ b/final_data_pipeline/output/325212_elec_options.xlsx
@@ -801,7 +801,7 @@
         <v>74</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE2">
         <v>8000</v>
@@ -896,7 +896,7 @@
         <v>74</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE3">
         <v>8000</v>
@@ -991,7 +991,7 @@
         <v>74</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE4">
         <v>8000</v>
@@ -1086,7 +1086,7 @@
         <v>74</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE5">
         <v>8000</v>
@@ -1181,7 +1181,7 @@
         <v>74</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE6">
         <v>8000</v>
@@ -1276,7 +1276,7 @@
         <v>74</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE7">
         <v>8000</v>
@@ -1371,7 +1371,7 @@
         <v>74</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE8">
         <v>8000</v>
@@ -1466,7 +1466,7 @@
         <v>74</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE9">
         <v>8000</v>
@@ -1561,7 +1561,7 @@
         <v>74</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE10">
         <v>8000</v>
@@ -1656,7 +1656,7 @@
         <v>74</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE11">
         <v>8000</v>
@@ -1751,7 +1751,7 @@
         <v>74</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -1846,7 +1846,7 @@
         <v>74</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -4221,7 +4221,7 @@
         <v>74</v>
       </c>
       <c r="AD38">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE38">
         <v>8000</v>
@@ -4316,7 +4316,7 @@
         <v>74</v>
       </c>
       <c r="AD39">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE39">
         <v>8000</v>
@@ -4411,7 +4411,7 @@
         <v>74</v>
       </c>
       <c r="AD40">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE40">
         <v>8000</v>
@@ -4506,7 +4506,7 @@
         <v>74</v>
       </c>
       <c r="AD41">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE41">
         <v>8000</v>
@@ -4601,7 +4601,7 @@
         <v>74</v>
       </c>
       <c r="AD42">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE42">
         <v>8000</v>
@@ -4696,7 +4696,7 @@
         <v>74</v>
       </c>
       <c r="AD43">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE43">
         <v>8000</v>
@@ -4791,7 +4791,7 @@
         <v>74</v>
       </c>
       <c r="AD44">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE44">
         <v>8000</v>
@@ -4886,7 +4886,7 @@
         <v>74</v>
       </c>
       <c r="AD45">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE45">
         <v>8000</v>
@@ -4981,7 +4981,7 @@
         <v>74</v>
       </c>
       <c r="AD46">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE46">
         <v>8000</v>
@@ -5076,7 +5076,7 @@
         <v>74</v>
       </c>
       <c r="AD47">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE47">
         <v>8000</v>
@@ -5171,7 +5171,7 @@
         <v>74</v>
       </c>
       <c r="AD48">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE48">
         <v>8000</v>
@@ -5266,7 +5266,7 @@
         <v>74</v>
       </c>
       <c r="AD49">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE49">
         <v>8000</v>
@@ -5361,7 +5361,7 @@
         <v>74</v>
       </c>
       <c r="AD50">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE50">
         <v>8000</v>
@@ -5456,7 +5456,7 @@
         <v>74</v>
       </c>
       <c r="AD51">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE51">
         <v>8000</v>
@@ -5551,7 +5551,7 @@
         <v>74</v>
       </c>
       <c r="AD52">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE52">
         <v>8000</v>
@@ -5646,7 +5646,7 @@
         <v>74</v>
       </c>
       <c r="AD53">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE53">
         <v>8000</v>
@@ -7261,7 +7261,7 @@
         <v>74</v>
       </c>
       <c r="AD70">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE70">
         <v>8000</v>
@@ -7356,7 +7356,7 @@
         <v>74</v>
       </c>
       <c r="AD71">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE71">
         <v>8000</v>
@@ -7451,7 +7451,7 @@
         <v>74</v>
       </c>
       <c r="AD72">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE72">
         <v>8000</v>
@@ -7546,7 +7546,7 @@
         <v>74</v>
       </c>
       <c r="AD73">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE73">
         <v>8000</v>
